--- a/TPDB_NO/analysis_for_TPDB_NO.xlsx
+++ b/TPDB_NO/analysis_for_TPDB_NO.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Danzel\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\repo\TerminationDatabase\TPDB_NO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD0AAD4-8068-4B28-99D4-060F15538F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCA3C33-BAA0-45DD-B05E-A173FAD7615A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="18720" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9171" yWindow="0" windowWidth="9429" windowHeight="11709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="无递归" sheetId="2" r:id="rId1"/>
+    <sheet name="包含部分递归" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="15">
   <si>
     <t>LLM</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -417,6 +418,114 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8976A8E-6EB8-4872-AF66-0942891CA346}">
+  <dimension ref="B2:G6"/>
+  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>34</v>
+      </c>
+      <c r="D3">
+        <v>48</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>89</v>
+      </c>
+      <c r="G3">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>31</v>
+      </c>
+      <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>68</v>
+      </c>
+      <c r="G4">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>53</v>
+      </c>
+      <c r="D5">
+        <v>29</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>89</v>
+      </c>
+      <c r="G5">
+        <v>10.79</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>59</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H28"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>

--- a/TPDB_NO/analysis_for_TPDB_NO.xlsx
+++ b/TPDB_NO/analysis_for_TPDB_NO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\repo\TerminationDatabase\TPDB_NO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCA3C33-BAA0-45DD-B05E-A173FAD7615A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6891A45-A5A9-41C5-9B3D-11164D92EA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9171" yWindow="0" windowWidth="9429" windowHeight="11709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,19 +447,21 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>89</v>
+        <f>C3+D3+E3</f>
+        <v>76</v>
       </c>
       <c r="G3">
-        <v>5.35</v>
+        <f>(24*5.36+6*6.13+46*5.1)/(24+6+46)</f>
+        <v>5.2634210526315783</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
@@ -467,19 +469,21 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>68</v>
+        <f t="shared" ref="F4:F5" si="0">C4+D4+E4</f>
+        <v>60</v>
       </c>
       <c r="G4">
-        <v>0.91</v>
+        <f>(17*0.9+8*0.91+35*0.94)/60</f>
+        <v>0.92466666666666675</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
@@ -487,19 +491,21 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>89</v>
+        <f t="shared" si="0"/>
+        <v>58</v>
       </c>
       <c r="G5">
-        <v>10.79</v>
+        <f>(25*9.94+3*16.33+30*10.31)/58</f>
+        <v>10.461896551724138</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
@@ -516,6 +522,7 @@
         <v>18</v>
       </c>
       <c r="F6">
+        <f>C6+D6+E6</f>
         <v>110</v>
       </c>
     </row>
